--- a/output.xlsx
+++ b/output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>越南文</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>菲律宾语</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -478,7 +483,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ano ang panahon ngayon?</t>
+          <t>Hôm nay thời tiết như thế nào?</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Anong panahon ngayon?</t>
         </is>
       </c>
     </row>
@@ -505,7 +515,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong maghanap ng mga flight bukas?</t>
+          <t>Bạn có thể giúp tôi tìm chuyến bay ngày mai không?</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pwede mo ba akong tulungan maghanap ng mga flight bukas?</t>
         </is>
       </c>
     </row>
@@ -532,6 +547,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Gần đây có nhà hàng nào ngon không?</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>May magagandang restaurant ba malapit dito?</t>
         </is>
       </c>
@@ -559,6 +579,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Bây giờ là mấy giờ ở Bắc Kinh?</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Anong oras na sa Beijing ngayon?</t>
         </is>
       </c>
@@ -586,7 +611,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maaari ka bang magkwento ng joke?</t>
+          <t>Bạn có thể kể cho tôi một câu chuyện cười không?</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pwede ka bang magkwento ng joke?</t>
         </is>
       </c>
     </row>
@@ -613,6 +643,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Rạp chiếu phim gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Saan ang pinakamalapit na sinehan?</t>
         </is>
       </c>
@@ -640,7 +675,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Anong oras ang sunrise bukas?</t>
+          <t>Ngày mai mặt trời mọc lúc mấy giờ?</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Anong oras ang pagsikat ng araw bukas?</t>
         </is>
       </c>
     </row>
@@ -667,7 +707,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong magsulat ng isang maikling tula?</t>
+          <t>Bạn có thể giúp tôi viết một bài thơ ngắn không?</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pwede mo ba akong tulungan magsulat ng isang maiksing tula?</t>
         </is>
       </c>
     </row>
@@ -694,7 +739,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>May park ba malapit dito na pwede maglakad-lakad?</t>
+          <t>Gần đây có công viên nào để đi dạo không?</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>May park ba malapit dito na pwede paglakaran?</t>
         </is>
       </c>
     </row>
@@ -721,7 +771,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ano ang pinakabagong produkto ng Apple?</t>
+          <t>Sản phẩm mới nhất mà Apple vừa ra mắt là gì?</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ano ang pinakabagong inilabas na produkto ng Apple?</t>
         </is>
       </c>
     </row>
@@ -748,7 +803,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maaari mo bang irekomenda sa akin ang isang magandang libro?</t>
+          <t>Bạn có thể gợi ý cho tôi một cuốn sách hay không?</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pwede ka bang mag-recommend ng magandang libro?</t>
         </is>
       </c>
     </row>
@@ -775,6 +835,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Thư viện gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Saan ang pinakamalapit na library?</t>
         </is>
       </c>
@@ -802,7 +867,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sino ang World Boxing Champion?</t>
+          <t>Ai là người sáng lập ra Wikipedia?</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sino ang mga miyembro ng World Cup?</t>
         </is>
       </c>
     </row>
@@ -829,7 +899,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong magdisenyo ng isang simpleng logo?</t>
+          <t>Bạn có thể giúp tôi thiết kế một logo đơn giản không?</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pwede mo ba akong tulungan mag-design ng simpleng logo?</t>
         </is>
       </c>
     </row>
@@ -856,7 +931,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saan ang pinakamalapit na museum?</t>
+          <t>Bảo tàng gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Saan ang pinakamalapit na museo?</t>
         </is>
       </c>
     </row>
@@ -883,6 +963,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Dòng sông dài nhất ở Trung Quốc là dòng sông nào?</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Alin ang pinakamahabang ilog sa China?</t>
         </is>
       </c>
@@ -910,7 +995,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maaari mo bang ipaliwanag sa akin ang quantum physics?</t>
+          <t>Bạn có thể giải thích cho tôi về cơ học lượng tử không?</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pwede mo ba akong tulungan ipaliwanag ang quantum physics?</t>
         </is>
       </c>
     </row>
@@ -937,6 +1027,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Bưu điện gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Saan ang pinakamalapit na post office?</t>
         </is>
       </c>
@@ -964,7 +1059,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ano ang pinaka-trending na palabas sa TV ngayon?</t>
+          <t>Gần đây có bộ phim truyền hình nào hay không?</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Anong trending na palabas sa TV ngayon?</t>
         </is>
       </c>
     </row>
@@ -991,7 +1091,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong gumawa ng isang presentasyon?</t>
+          <t>Bạn có thể giúp tôi làm một bài thuyết trình PowerPoint không?</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pwede mo ba akong tulungan gumawa ng isang presentation?</t>
         </is>
       </c>
     </row>
@@ -1018,6 +1123,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Phòng tập thể dục gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Saan ang pinakamalapit na gym?</t>
         </is>
       </c>
@@ -1045,7 +1155,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ano ang mga bagong laro na inilabas kamakailan?</t>
+          <t>Gần đây có game nào mới ra mắt không?</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Anong bagong games ang inilabas kamakailan?</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1187,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong magsulat ng isang application letter?</t>
+          <t>Bạn có thể giúp tôi viết một lá thư xin việc không?</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pwede mo ba akong tulungan magsulat ng application letter?</t>
         </is>
       </c>
     </row>
@@ -1099,6 +1219,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Quán bar gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>Saan ang pinakamalapit na bar?</t>
         </is>
       </c>
@@ -1126,7 +1251,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ano ang pinakamalapit na concert?</t>
+          <t>Buổi biểu diễn gần nhất là gì?</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Anong concert ang mayroon kamakailan?</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1283,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong isalin ang isang artikulo sa Ingles?</t>
+          <t>Bạn có thể giúp tôi dịch một bài báo tiếng Anh không?</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pwede mo ba akong tulungan i-translate ang isang artikulo sa Ingles?</t>
         </is>
       </c>
     </row>
@@ -1180,6 +1315,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Quán cà phê gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>Saan ang pinakamalapit na coffee shop?</t>
         </is>
       </c>
@@ -1207,7 +1347,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ano ang pinakamalapit na art exhibit?</t>
+          <t>Triển lãm gần nhất là gì?</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Anong exhibit ang mayroon kamakailan?</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1379,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong magsulat ng isang sanaysay tungkol sa artificial intelligence?</t>
+          <t>Bạn có thể giúp tôi viết một bài luận về trí tuệ nhân tạo không?</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pwede mo ba akong tulungan magsulat ng isang sanaysay tungkol sa artificial intelligence?</t>
         </is>
       </c>
     </row>
@@ -1261,6 +1411,11 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>Ngân hàng gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>Saan ang pinakamalapit na bangko?</t>
         </is>
       </c>
@@ -1288,6 +1443,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>Dự báo thời tiết ngày mai như thế nào?</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>Ano ang weather forecast bukas?</t>
         </is>
       </c>
@@ -1315,7 +1475,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong suriin ang iskedyul ng mga flight?</t>
+          <t>Bạn có thể giúp tôi kiểm tra lịch trình xe buýt không?</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong maghanap ng schedule ng mga flight?</t>
         </is>
       </c>
     </row>
@@ -1342,6 +1507,11 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>Gần đây có cửa hàng nào để mua sắm không?</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>May mga malapit bang mall kung saan ako makakabili ng mga gamit?</t>
         </is>
       </c>
@@ -1369,6 +1539,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>Tình hình thị trường chứng khoán gần đây thế nào?</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>Ano ang mga pinakahuling balita sa stock market?</t>
         </is>
       </c>
@@ -1396,6 +1571,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>Bạn có thể giúp tôi thiết kế một trang web đơn giản không?</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>Maaari mo bang tulungan akong magdisenyo ng isang simpleng website?</t>
         </is>
       </c>
@@ -1423,7 +1603,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saan ang pinakahuling mga supermarket?</t>
+          <t>Siêu thị gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nasaan ang pinakamalapit na supermarket?</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1635,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ano ang mga pinakahuling inilabas na mga produktong teknolohikal?</t>
+          <t>Gần đây có sản phẩm công nghệ mới nào được ra mắt không?</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ano ang mga pinakahuling inilunsad na mga produktong teknolohikal?</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1667,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang product description?</t>
+          <t>Bạn có thể giúp tôi viết một bài thuyết minh sản phẩm không?</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang product description?</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1699,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saan ang pinaka-malapit na gasolinahan?</t>
+          <t>Trạm xăng gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Saan ang pinakamalapit na gasolinahan?</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1731,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ano ang mga pinakahuling inilabas na mga cellphone?</t>
+          <t>Gần đây có điện thoại di động mới nào được ra mắt không?</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ano ang mga pinakahuling inilunsad na mga bagong cellphone?</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1763,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang news report?</t>
+          <t>Bạn có thể giúp tôi viết một bài báo cáo tin tức không?</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang news report?</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1795,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saan ang pinaka-malapit na parmasya?</t>
+          <t>Nhà thuốc gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Saan ang pinakamalapit na botika?</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1827,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ano ang mga pinakahuling inilabas na sasakyan?</t>
+          <t>Gần đây có ô tô mới nào được ra mắt không?</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ano ang mga pinakahuling inilunsad na mga bagong sasakyan?</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1859,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang market research report?</t>
+          <t>Bạn có thể giúp tôi viết một báo cáo nghiên cứu thị trường không?</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang market research report?</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1891,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saan ang pinaka-malapit na ospital?</t>
+          <t>Bệnh viện gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Saan ang pinakamalapit na ospital?</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1923,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ano ang mga pinakahuling inilabas na pelikula?</t>
+          <t>Gần đây có phim mới nào được chiếu không?</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ano ang mga pinakahuling inilabas na mga bagong pelikula?</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1955,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang business plan?</t>
+          <t>Bạn có thể giúp tôi viết một kế hoạch kinh doanh không?</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang business plan?</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1987,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saan ang pinaka-malapit na paaralan?</t>
+          <t>Trường học gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Saan ang pinakamalapit na paaralan?</t>
         </is>
       </c>
     </row>
@@ -1774,7 +2019,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ano ang mga pinakahuling inilabas na mga event sa entertainment?</t>
+          <t>Gần đây có sự kiện văn hóa nào mới không?</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ano ang mga pinakahuling event sa arts and culture?</t>
         </is>
       </c>
     </row>
@@ -1801,7 +2051,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang script para sa isang speech?</t>
+          <t>Bạn có thể giúp tôi viết một bài diễn thuyết không?</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang speech?</t>
         </is>
       </c>
     </row>
@@ -1828,7 +2083,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saan ang pinaka-malapit na branch ng library?</t>
+          <t>Thư viện gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Saan ang pinakamalapit na library branch?</t>
         </is>
       </c>
     </row>
@@ -1855,7 +2115,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ano ang mga pinakahuling inilabas na mga album ng musika?</t>
+          <t>Gần đây có album nhạc mới nào được phát hành không?</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ano ang mga pinakahuling inilabas na mga bagong album ng musika?</t>
         </is>
       </c>
     </row>
@@ -1882,7 +2147,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang scientific essay?</t>
+          <t>Bạn có thể giúp tôi viết một bài luận khoa học không?</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang scientific paper?</t>
         </is>
       </c>
     </row>
@@ -1909,7 +2179,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saan ang pinaka-malapit na entrance ng park?</t>
+          <t>Công viên gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Saan ang pinakamalapit na park entrance?</t>
         </is>
       </c>
     </row>
@@ -1936,7 +2211,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ano ang mga pinakahuling inilabas na mga art exhibition?</t>
+          <t>Gần đây có triển lãm nghệ thuật mới nào không?</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ano ang mga pinakahuling art exhibition?</t>
         </is>
       </c>
     </row>
@@ -1963,7 +2243,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang literary criticism?</t>
+          <t>Bạn có thể giúp tôi viết một bài phê bình văn học không?</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang literary criticism?</t>
         </is>
       </c>
     </row>
@@ -1990,7 +2275,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saan ang pinaka-malapit na souvenir shop ng museum?</t>
+          <t>Cửa hàng lưu niệm bảo tàng gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Saan ang pinakamalapit na museum gift shop?</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2307,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ano ang mga pinakahuling inilabas na mga sports event?</t>
+          <t>Gần đây có sự kiện thể thao mới nào không?</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ano ang mga pinakahuling sports event?</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2339,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang movie review?</t>
+          <t>Bạn có thể giúp tôi viết một bài đánh giá phim không?</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang movie review?</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2371,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saan ang pinaka-malapit na gym?</t>
+          <t>Khu vực thiết bị thể dục gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Saan ang pinakamalapit na gym?</t>
         </is>
       </c>
     </row>
@@ -2098,6 +2403,11 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>Gần đây có những đột phá công nghệ mới nào?</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>Ano ang mga pinakabagong pagsulong sa teknolohiya?</t>
         </is>
       </c>
@@ -2125,7 +2435,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang pagsusuri sa libro?</t>
+          <t>Bạn có thể giúp tôi viết một bài đánh giá sách không?</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang review ng libro?</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2467,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saan ang pinakamalapit na bar na may swimming pool?</t>
+          <t>Quán bar, bể bơi gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Saan ang pinakamalapit na swimming pool ng bar?</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2499,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ano ang mga pinakabagong pagsulong sa teknolohiyang pangkapaligiran?</t>
+          <t>Gần đây có những công nghệ bảo vệ môi trường mới nào?</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ano ang mga pinakabagong pagsulong sa teknolohiyang pangkalikasan?</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2531,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang post sa social media?</t>
+          <t>Bạn có thể giúp tôi viết một bài đăng trên diễn đàn không?</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang post sa social media?</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2563,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saan ang pinakamalapit na coffee shop na may outdoor seating?</t>
+          <t>Quán cà phê ngoài trời gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Saan ang pinakamalapit na outdoor seating ng coffee shop?</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2595,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ano ang mga pinakabagong patakaran sa enerhiya?</t>
+          <t>Gần đây có những chính sách năng lượng mới nào?</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ano ang mga pinakabagong polisiya sa enerhiya?</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2627,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang post sa social media?</t>
+          <t>Bạn có thể giúp tôi viết một bài đăng trên mạng xã hội không?</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang post sa social media?</t>
         </is>
       </c>
     </row>
@@ -2314,6 +2659,11 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>Máy ATM ngân hàng gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>Saan ang pinakamalapit na ATM machine ng bangko?</t>
         </is>
       </c>
@@ -2341,6 +2691,11 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>Gần đây có những cải cách giáo dục mới nào?</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>Ano ang mga pinakabagong reporma sa edukasyon?</t>
         </is>
       </c>
@@ -2368,7 +2723,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang email?</t>
+          <t>Bạn có thể giúp tôi viết một email không?</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang email?</t>
         </is>
       </c>
     </row>
@@ -2395,6 +2755,11 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>Bãi đỗ xe ngoài trời gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>Saan ang pinakamalapit na parking lot ng mall?</t>
         </is>
       </c>
@@ -2422,7 +2787,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ano ang mga pinakabagong pag-unlad sa medisina?</t>
+          <t>Gần đây có những tiến bộ y tế mới nào?</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Ano ang mga pinakabagong pagsulong sa medisina?</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2819,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang text message?</t>
+          <t>Bạn có thể giúp tôi viết một tin nhắn ngắn không?</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang text message?</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2851,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saan ang pinakamalapit na gasolinahan na may clinic?</t>
+          <t>Trạm xăng y tế gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Saan ang pinakamalapit na 24 oras na klinika?</t>
         </is>
       </c>
     </row>
@@ -2503,6 +2883,11 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>Gần đây có những vấn đề xã hội mới nào?</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>Ano ang mga pinakabagong isyu sa lipunan?</t>
         </is>
       </c>
@@ -2530,7 +2915,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang survey questionnaire?</t>
+          <t>Bạn có thể giúp tôi viết một bảng câu hỏi không?</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang survey questionnaire?</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2947,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saan ang pinakamalapit na botika na may emergency room?</t>
+          <t>Phòng cấp cứu bệnh viện gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Saan ang pinakamalapit na emergency room ng botika?</t>
         </is>
       </c>
     </row>
@@ -2584,6 +2979,11 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>Gần đây có những sự kiện chính trị mới nào?</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>Ano ang mga pinakabagong pangyayari sa politika?</t>
         </is>
       </c>
@@ -2611,7 +3011,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang ulat?</t>
+          <t>Bạn có thể giúp tôi viết một bản báo cáo không?</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang ulat?</t>
         </is>
       </c>
     </row>
@@ -2638,7 +3043,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saan ang pinakamalapit na ospital na may emergency room?</t>
+          <t>Phòng cấp cứu bệnh viện gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Saan ang pinakamalapit na emergency room ng ospital?</t>
         </is>
       </c>
     </row>
@@ -2665,7 +3075,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ano ang mga pinakabagong kalagayan sa ekonomiya?</t>
+          <t>Gần đây có những xu hướng kinh tế mới nào?</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Ano ang mga pinakabagong kalakaran sa ekonomiya?</t>
         </is>
       </c>
     </row>
@@ -2692,7 +3107,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang buod?</t>
+          <t>Bạn có thể giúp tôi viết một bản tóm tắt không?</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang buod?</t>
         </is>
       </c>
     </row>
@@ -2719,6 +3139,11 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>Thư viện trường học gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t>Saan ang pinakamalapit na library ng paaralan?</t>
         </is>
       </c>
@@ -2746,7 +3171,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ano ang mga pinakabagong penomena sa kultura?</t>
+          <t>Gần đây có những hiện tượng văn hóa mới nào?</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Ano ang mga pinakabagong pangyayari sa sining?</t>
         </is>
       </c>
     </row>
@@ -2773,7 +3203,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang plano?</t>
+          <t>Bạn có thể giúp tôi viết một kế hoạch không?</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang business plan?</t>
         </is>
       </c>
     </row>
@@ -2800,6 +3235,11 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>Phòng tự học thư viện gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>Saan ang pinakamalapit na self-study room ng library?</t>
         </is>
       </c>
@@ -2827,6 +3267,11 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>Gần đây có những xu hướng nghệ thuật mới nào?</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>Ano ang mga pinakabagong uso sa sining?</t>
         </is>
       </c>
@@ -2854,7 +3299,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Maaari mo bang tulungan akong sumulat ng isang projection?</t>
+          <t>Bạn có thể giúp tôi viết một bảng dự toán không?</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Maaari mo bang tulungan akong magsulat ng isang proforma invoice?</t>
         </is>
       </c>
     </row>
@@ -2881,7 +3331,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saan ang pinakamalapit na playground sa parke?</t>
+          <t>Khu vui chơi trẻ em công cộng gần nhất ở đâu?</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Saan ang pinakamalapit na playground ng parke?</t>
         </is>
       </c>
     </row>
